--- a/v3/example/xlsx/Type.xlsx
+++ b/v3/example/xlsx/Type.xlsx
@@ -1171,7 +1171,7 @@
     <col min="5" max="5" width="11.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1198,6 +1198,11 @@
       </c>
       <c r="I1" s="2" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>#备注</t>
+        </is>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:11">
